--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -744,7 +744,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -756,7 +758,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -768,7 +772,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -780,7 +786,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -792,7 +800,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -804,7 +814,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -816,7 +828,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -828,7 +842,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -840,7 +856,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -852,7 +870,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -864,7 +884,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -876,7 +898,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -888,7 +912,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -900,7 +926,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -912,7 +940,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -924,7 +954,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -936,7 +968,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -948,7 +982,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -960,7 +996,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -972,7 +1010,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -984,7 +1024,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -996,7 +1038,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -1008,7 +1052,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -1020,7 +1066,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1032,7 +1080,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1044,7 +1094,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1056,7 +1108,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1068,7 +1122,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1080,7 +1136,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1092,7 +1150,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1104,7 +1164,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1116,7 +1178,9 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1128,7 +1192,9 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1140,7 +1206,9 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1152,7 +1220,9 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1164,7 +1234,9 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1176,7 +1248,9 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -1188,7 +1262,9 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -1200,7 +1276,9 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -1212,7 +1290,9 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -1224,7 +1304,9 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -1236,7 +1318,9 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -1248,7 +1332,9 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-code-tarif-tnjp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
